--- a/public/templates/master-template.xlsx
+++ b/public/templates/master-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Invoice" sheetId="1" r:id="rId1"/>
+    <sheet name="Tax Invoice" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -66,8 +66,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -404,500 +405,526 @@
   <dimension ref="A1:G50"/>
   <cols>
     <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="4.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="B1" t="str">
-        <v>INVOICE</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="str">
-        <v>Company Name:</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Your Business Name</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Invoice Number:</v>
-      </c>
-      <c r="F3" t="str">
-        <v>INV-001</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>TAX INVOICE</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="str">
+        <v>Generated by InvoiceGenerator.ng — Free Invoice Generator for Nigerian Businesses</v>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="18" customHeight="1">
       <c r="B4" t="str">
-        <v>Address:</v>
-      </c>
-      <c r="C4" t="str">
-        <v>123 Business Street</v>
+        <v>COMPANY INFORMATION</v>
       </c>
       <c r="E4" t="str">
-        <v>Invoice Date:</v>
+        <v>INVOICE DETAILS</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="str">
-        <v>City / State:</v>
+        <v>Company Name:</v>
       </c>
       <c r="C5" t="str">
-        <v>Lagos, Nigeria</v>
+        <v>Your Business Name</v>
       </c>
       <c r="E5" t="str">
-        <v>Due Date:</v>
+        <v>Invoice Number:</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>INV-001</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
-        <v>Phone:</v>
+        <v>Address:</v>
       </c>
       <c r="C6" t="str">
-        <v>+234 800 000 0000</v>
+        <v>123 Business Street</v>
       </c>
       <c r="E6" t="str">
-        <v>Purchase Order:</v>
+        <v>Invoice Date:</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>Apr 17, 2026</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="str">
-        <v>Email:</v>
+        <v>City / State:</v>
       </c>
       <c r="C7" t="str">
-        <v>hello@yourbusiness.com</v>
+        <v>Lagos Island, Lagos State</v>
       </c>
       <c r="E7" t="str">
-        <v>Currency:</v>
+        <v>Due Date:</v>
       </c>
       <c r="F7" t="str">
-        <v>NGN (₦)</v>
+        <v>May 17, 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="str">
-        <v>Website:</v>
+        <v>Phone:</v>
       </c>
       <c r="C8" t="str">
-        <v>www.yourbusiness.com</v>
+        <v>+234 800 000 0000</v>
+      </c>
+      <c r="E8" t="str">
+        <v>PO Number:</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PO-2026-042</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="str">
+        <v>Email:</v>
+      </c>
+      <c r="C9" t="str">
+        <v>hello@yourbusiness.com</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Currency:</v>
+      </c>
+      <c r="F9" t="str">
+        <v>NGN (₦)</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="str">
-        <v>BILL TO</v>
+        <v>Website:</v>
+      </c>
+      <c r="C10" t="str">
+        <v>www.yourbusiness.com</v>
       </c>
       <c r="E10" t="str">
-        <v>SHIP TO (optional)</v>
+        <v>Status:</v>
+      </c>
+      <c r="F10" t="str">
+        <v>UNPAID</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="str">
-        <v>Client Name:</v>
+        <v>TIN:</v>
       </c>
       <c r="C11" t="str">
-        <v>Client Company Name</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Client Name:</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
+        <v>00000000</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="str">
-        <v>Address:</v>
+        <v>VAT Reg (VRN):</v>
       </c>
       <c r="C12" t="str">
-        <v>456 Client Street</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Address:</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
+        <v>VRN-00000000-0001</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="str">
+        <v>CAC (RC No):</v>
+      </c>
+      <c r="C13" t="str">
+        <v>1234567</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" t="str">
+        <v>BILL TO</v>
+      </c>
+      <c r="E15" t="str">
+        <v>PAYMENT / BANK DETAILS</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>Client Name:</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Acme Nigeria Limited</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Bank Name:</v>
+      </c>
+      <c r="F16" t="str">
+        <v>First Bank of Nigeria</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>Address:</v>
+      </c>
+      <c r="C17" t="str">
+        <v>45 Victoria Island Boulevard</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Account Name:</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Your Business Name</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="str">
         <v>City / State:</v>
       </c>
-      <c r="C13" t="str">
-        <v>Abuja, Nigeria</v>
-      </c>
-      <c r="E13" t="str">
-        <v>City / State:</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="str">
+      <c r="C18" t="str">
+        <v>Victoria Island, Lagos</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Account Number:</v>
+      </c>
+      <c r="F18" t="str">
+        <v>0123456789</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="str">
         <v>Phone:</v>
       </c>
-      <c r="C14" t="str">
-        <v>+234 800 000 0000</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Phone:</v>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="str">
+      <c r="C19" t="str">
+        <v>+234 802 345 6789</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Sort Code:</v>
+      </c>
+      <c r="F19" t="str">
+        <v>011</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
         <v>Email:</v>
       </c>
-      <c r="C15" t="str">
-        <v>client@company.com</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Email:</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="B17" t="str">
+      <c r="C20" t="str">
+        <v>accounts@acmenigeria.com</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Payment Terms:</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Net 30 Days</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="str">
+        <v>Client TIN:</v>
+      </c>
+      <c r="C21" t="str">
+        <v>11111111</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" t="str">
         <v>#</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C23" t="str">
         <v>Description</v>
       </c>
-      <c r="E17" t="str">
+      <c r="E23" t="str">
         <v>Qty</v>
       </c>
-      <c r="F17" t="str">
-        <v>Rate (₦)</v>
-      </c>
-      <c r="G17" t="str">
+      <c r="F23" t="str">
+        <v>Unit Price (₦)</v>
+      </c>
+      <c r="G23" t="str">
         <v>Amount (₦)</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Service / Product Description</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1">
-        <f>E18*F18</f>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <f>E19*F19</f>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <f>E20*F20</f>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <f>E21*F21</f>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <f>E22*F22</f>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <f>E23*F23</f>
       </c>
     </row>
     <row r="24">
       <c r="B24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
+        <v>Website Design &amp; Development</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>250000</v>
+      </c>
+      <c r="G24" s="2">
         <f>E24*F24</f>
       </c>
     </row>
     <row r="25">
       <c r="B25">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
+        <v>Monthly Hosting &amp; Maintenance</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G25" s="2">
         <f>E25*F25</f>
       </c>
     </row>
     <row r="26">
       <c r="B26">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
+        <v>SEO Optimisation Package</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G26" s="2">
         <f>E26*F26</f>
       </c>
     </row>
     <row r="27">
       <c r="B27">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
         <f>E27*F27</f>
       </c>
     </row>
+    <row r="28">
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <f>E28*F28</f>
+      </c>
+    </row>
     <row r="29">
-      <c r="E29" t="str">
-        <v>Subtotal (₦):</v>
-      </c>
-      <c r="G29" s="1">
-        <f>SUM(G18:G27)</f>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <f>E29*F29</f>
       </c>
     </row>
     <row r="30">
-      <c r="E30" t="str">
-        <v>Discount (%):</v>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="E30" s="1">
+        <v>0</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="1">
-        <f>ROUND(G29*F30/100,2)</f>
+      <c r="G30" s="2">
+        <f>E30*F30</f>
       </c>
     </row>
     <row r="31">
-      <c r="E31" t="str">
-        <v>VAT (7.5%):</v>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
       </c>
       <c r="F31" s="2">
-        <v>7.5</v>
-      </c>
-      <c r="G31" s="1">
-        <f>ROUND((G29-G30)*F31/100,2)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <f>E31*F31</f>
       </c>
     </row>
     <row r="32">
-      <c r="E32" t="str">
-        <v>Shipping (₦):</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
+      <c r="B32">
+        <v>9</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <f>E32*F32</f>
       </c>
     </row>
     <row r="33">
-      <c r="E33" t="str">
-        <v>TOTAL DUE (₦):</v>
-      </c>
-      <c r="G33" s="1">
-        <f>G29-G30+G31+G32</f>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" t="str">
-        <v>Amount Paid (₦):</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-    </row>
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <f>E33*F33</f>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="E35" t="str">
+        <v>Subtotal (₦):</v>
+      </c>
+      <c r="G35" s="2">
+        <f>SUM(G24:G33)</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" t="str">
+        <v>Discount (%):</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <f>ROUND(G35*F36/100,2)</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" t="str">
+        <v>VAT (%):</v>
+      </c>
+      <c r="F37" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="G37" s="2">
+        <f>ROUND((G35-G36)*F37/100,2)</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="E38" t="str">
+        <v>Shipping (₦):</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="E39" t="str">
+        <v>TOTAL DUE (₦):</v>
+      </c>
+      <c r="G39" s="2">
+        <f>G35-G36+G37+G38</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="E40" t="str">
+        <v>Amount Paid (₦):</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="E41" t="str">
         <v>Balance Due (₦):</v>
       </c>
-      <c r="G35" s="1">
-        <f>G33-G34</f>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="str">
-        <v>PAYMENT / BANK DETAILS</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="str">
-        <v>Bank Name:</v>
-      </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="str">
-        <v>Account Name:</v>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="str">
-        <v>Account Number:</v>
-      </c>
-      <c r="C40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="str">
-        <v>Sort Code / IBAN:</v>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="str">
-        <v>NOTES</v>
-      </c>
-    </row>
+      <c r="G41" s="2">
+        <f>G39-G40</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="E42" t="str">
+        <v>VAT per FIRS regulations (VAT Act Cap. V1 LFN 2004)</v>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="B44" t="str">
-        <v>Thank you for your business!</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="str">
-        <v>TERMS &amp; CONDITIONS</v>
-      </c>
-    </row>
+        <v>NOTES</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="str">
+        <v>Thank you for your business! Please reference the invoice number on your payment.</v>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" t="str">
-        <v>Payment is due within 30 days of invoice date. Late payments may attract a 5% monthly charge.</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="str">
-        <v>Generated by InvoiceGenerator.ng — Free Invoice Generator for Nigerian Businesses</v>
-      </c>
-    </row>
+        <v>TERMS &amp; CONDITIONS</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="str">
+        <v>Payment due within 30 days of invoice date. A 1.5% per month late fee applies to overdue balances. Disputes must be raised within 7 days of receipt.</v>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
+  <mergeCells count="16">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B48:G48"/>
   </mergeCells>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
